--- a/data/seed/portfolio/L-2025-6310/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-6310/vypiska_2026-07_09.xlsx
@@ -542,21 +542,21 @@
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>736000</v>
+        <v>5539000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nurafshon Un Mahsulotlari MChJ</t>
+          <t>Farovon Metall MChJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>259691263</t>
+          <t>348767200</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000985509924001</t>
+          <t>20208000587984937001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -566,131 +566,131 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №6949 от 01.07.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7021 01.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>26136000</v>
+        <v>30939000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n">
-        <v>8831000</v>
+        <v>3206000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Farovon Metall MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>348767200</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000587984937001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4482</t>
+          <t>Shartnoma №22/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>34967000</v>
+        <v>34145000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n">
-        <v>1284000</v>
-      </c>
+      <c r="C10" s="2" t="n">
+        <v>6697000</v>
+      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bekobod Yog' Zavodi MChJ</t>
+          <t>Urganch Plastik AJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>309487672</t>
+          <t>304819265</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000015879849001</t>
+          <t>20208000431725759001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №83/26 ОТ 02.07.2026</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №154/26</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>36251000</v>
+        <v>27448000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>755000</v>
+        <v>15588000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №20/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7895</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>37006000</v>
+        <v>43036000</v>
       </c>
     </row>
     <row r="12">
@@ -700,77 +700,77 @@
       <c r="B12" t="n">
         <v>104</v>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>4649000</v>
-      </c>
-      <c r="D12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n">
+        <v>9322000</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bekobod Plastik XK</t>
+          <t>Farovon Metall MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>296048192</t>
+          <t>348767200</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000574317257001</t>
+          <t>20208000587984937001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №204/26</t>
+          <t>Shartnoma №125/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>32357000</v>
+        <v>52358000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>9950000</v>
+        <v>3698000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yangi Hayot Mato XK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>276362214</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000849952169001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4863</t>
+          <t>Shartnoma №94/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>42307000</v>
+        <v>56056000</v>
       </c>
     </row>
     <row r="14">
@@ -782,35 +782,35 @@
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>3023000</v>
+        <v>5394000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Afrosiyob Tekstil XK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>244637602</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000765267812001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №93/26 от 06.07.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №269/26, QQS 12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>45330000</v>
+        <v>61450000</v>
       </c>
     </row>
     <row r="15">
@@ -822,35 +822,35 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>1768000</v>
+        <v>3894000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nurafshon Un Mahsulotlari MChJ</t>
+          <t>Buxoro Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>259691263</t>
+          <t>245610193</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000985509924001</t>
+          <t>20208000141137934001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №2056 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4491 06.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>47098000</v>
+        <v>65344000</v>
       </c>
     </row>
     <row r="16">
@@ -860,37 +860,37 @@
       <c r="B16" t="n">
         <v>108</v>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n">
-        <v>1629000</v>
-      </c>
+      <c r="C16" s="2" t="n">
+        <v>6216000</v>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Buxoro Avto Ehtiyot MChJ</t>
+          <t>Chust Tekstil MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>225149335</t>
+          <t>273111718</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000417613774001</t>
+          <t>20208000892961939001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Shartnoma №284/26 bo'yicha oldindan to'lov</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №269/26</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>48727000</v>
+        <v>59128000</v>
       </c>
     </row>
     <row r="17">
@@ -900,37 +900,37 @@
       <c r="B17" t="n">
         <v>109</v>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n">
-        <v>1257000</v>
-      </c>
+      <c r="C17" s="2" t="n">
+        <v>11503000</v>
+      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Bahor Avto Savdo XK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>222269861</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000916909352001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №153/26, QQS 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №276/26</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>49984000</v>
+        <v>47625000</v>
       </c>
     </row>
     <row r="18">
@@ -941,36 +941,31 @@
         <v>110</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>2855000</v>
+        <v>15062000</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>250731117</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №119/26</t>
+          <t>Iyun oyi uchun ish haqi, reestr №8062</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>47129000</v>
+        <v>32563000</v>
       </c>
     </row>
     <row r="19">
@@ -981,57 +976,62 @@
         <v>111</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>4277000</v>
+        <v>24581000</v>
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Xiva Agro MChJ</t>
+          <t>Chust Tekstil MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>360222698</t>
+          <t>273111718</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000139169093001</t>
+          <t>20208000892961939001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №2345</t>
+          <t>Xom ashyo uchun to'lov, shartn. №28/26, QQS bilan</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>42852000</v>
+        <v>7982000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>15062000</v>
-      </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n">
+        <v>4178000</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Yulduz Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1041,11 +1041,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №9915</t>
+          <t>Shartnoma №268/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>27790000</v>
+        <v>12160000</v>
       </c>
     </row>
     <row r="21">
@@ -1057,35 +1057,35 @@
       </c>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n">
-        <v>5943000</v>
+        <v>3575000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №137/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №140/26, QQS 12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>33733000</v>
+        <v>15735000</v>
       </c>
     </row>
     <row r="22">
@@ -1097,21 +1097,21 @@
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n">
-        <v>3957000</v>
+        <v>1719000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Afrosiyob Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>246402849</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000274674310001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1121,37 +1121,37 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №103/26 от 07.07.2026</t>
+          <t>Предоплата за товар по договору №213/26 от 07.07.2026</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>37690000</v>
+        <v>17454000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n">
-        <v>745000</v>
-      </c>
+      <c r="C23" s="2" t="n">
+        <v>1273000</v>
+      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Oltin Vodiy Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>335080958</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000573454594001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1161,251 +1161,251 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №237/26, НДС 12%</t>
+          <t>Bino ijarasi uchun to'lov iyul</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>38435000</v>
+        <v>16181000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>1273000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>6273000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nihol Qurilish MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>318350809</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000855734545001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Арендная плата за июль 2026 г. по договору №94/21</t>
+          <t>Оплата за товар по счет-фактуре №7500 от 09.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>37162000</v>
+        <v>22454000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>6192000</v>
+        <v>4897000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №55/26, НДС 12%</t>
+          <t>Shartnoma №262/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>43354000</v>
+        <v>27351000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n">
-        <v>1878000</v>
+        <v>3191000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №5721 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5914</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>45232000</v>
+        <v>30542000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
-      <c r="C27" s="2" t="n">
-        <v>4643000</v>
-      </c>
-      <c r="D27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n">
+        <v>1355000</v>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>250731117</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №83/26 от 08.07.2026, НДС 12%</t>
+          <t>Оплата по с/ф №5996 за поставленный товар</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>40589000</v>
+        <v>31897000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
-      <c r="C28" s="2" t="n">
-        <v>1418000</v>
-      </c>
-      <c r="D28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n">
+        <v>10503000</v>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
+          <t>Afrosiyob Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>250731117</t>
+          <t>246402849</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>20208000274674310001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №46/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3364 10.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>39171000</v>
+        <v>42400000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>5506000</v>
-      </c>
-      <c r="D29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n">
+        <v>1475000</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>250731117</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4602</t>
+          <t>Shartnoma №85/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>33665000</v>
+        <v>43875000</v>
       </c>
     </row>
     <row r="30">
@@ -1415,58 +1415,58 @@
       <c r="B30" t="n">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n">
-        <v>834000</v>
-      </c>
+      <c r="C30" s="2" t="n">
+        <v>10300000</v>
+      </c>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>235448476</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-6310)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>16307000223851930417</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8992 за поставленный товар</t>
+          <t>Kredit shartnomasi L-2025-6310 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>34499000</v>
+        <v>33575000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>10300000</v>
-      </c>
-      <c r="D31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n">
+        <v>1547000</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-6310)</t>
+          <t>Yulduz Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>16307000223851930417</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1476,131 +1476,131 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-6310 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Shartnoma №298/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>24199000</v>
+        <v>35122000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n">
-        <v>25594000</v>
+        <v>6536000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Navoiy Savdo MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>273446376</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000277652678001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №246/26 от 13.07.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5698 14.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>49793000</v>
+        <v>41658000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>5110000</v>
+        <v>2727000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №215/26, QQS 12%</t>
+          <t>Shartnoma №140/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>54903000</v>
+        <v>44385000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n">
-        <v>1062000</v>
-      </c>
+      <c r="C34" s="2" t="n">
+        <v>2054000</v>
+      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5525 за поставленный товар</t>
+          <t>Ijtimoiy soliq iyun 2026</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>55965000</v>
+        <v>42331000</v>
       </c>
     </row>
     <row r="35">
@@ -1610,463 +1610,463 @@
       <c r="B35" t="n">
         <v>127</v>
       </c>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n">
-        <v>14767000</v>
-      </c>
+      <c r="C35" s="2" t="n">
+        <v>2054000</v>
+      </c>
+      <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ilhom Agro MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>301067435</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000806702754001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №45/26, QQS 12%</t>
+          <t>JShDS iyun oyi uchun</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>70732000</v>
+        <v>40277000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="n">
-        <v>5247000</v>
+        <v>745000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №174/26, НДС 12%</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №265/26, QQS 12%</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>75979000</v>
+        <v>41022000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>2054000</v>
-      </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n">
+        <v>3777000</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Farovon Metall MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>348767200</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000587984937001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ijtimoiy soliq</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5611</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>73925000</v>
+        <v>44799000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>2054000</v>
-      </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n">
+        <v>1667000</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Afrosiyob Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>246402849</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000274674310001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №333 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>71871000</v>
+        <v>46466000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>4847000</v>
-      </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n">
+        <v>1203000</v>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>250731117</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7074</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6446</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>67024000</v>
+        <v>47669000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46217</v>
+        <v>46223</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
-      <c r="C40" s="2" t="n">
-        <v>8430000</v>
-      </c>
-      <c r="D40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n">
+        <v>4824000</v>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bekobod Plastik XK</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>296048192</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000574317257001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4685</t>
+          <t>SHARTNOMA №13/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>58594000</v>
+        <v>52493000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>2015000</v>
-      </c>
-      <c r="D41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n">
+        <v>1485000</v>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Navoiy Trans Servis MChJ</t>
+          <t>Afrosiyob Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>265557988</t>
+          <t>246402849</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000786983038001</t>
+          <t>20208000274674310001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №95/26, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2034 20.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>56579000</v>
+        <v>53978000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>11185000</v>
+        <v>1294000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №141/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №2482 20.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>67764000</v>
+        <v>55272000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n">
-        <v>4639000</v>
-      </c>
+      <c r="C43" s="2" t="n">
+        <v>9049000</v>
+      </c>
+      <c r="D43" s="2" t="n"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nurafshon Un Mahsulotlari MChJ</t>
+          <t>Urganch Plastik AJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>259691263</t>
+          <t>304819265</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000985509924001</t>
+          <t>20208000431725759001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2902 за поставленный товар</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №99/26, QQS bilan</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>72403000</v>
+        <v>46223000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n">
-        <v>914000</v>
-      </c>
+      <c r="C44" s="2" t="n">
+        <v>37990000</v>
+      </c>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Chust Tekstil MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>273111718</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000892961939001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №41/26, НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №271/26</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>73317000</v>
+        <v>8233000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n">
-        <v>6147000</v>
-      </c>
+      <c r="C45" s="2" t="n">
+        <v>2172000</v>
+      </c>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Guliston Metall Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>244456101</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000361411379001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8154 за поставленный товар</t>
+          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>79464000</v>
+        <v>6061000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n">
-        <v>3689000</v>
+        <v>1327000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Denov Meva-Sabzavot AJ</t>
+          <t>Omad Metall Servis XK</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>299118849</t>
+          <t>209936791</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000850814989001</t>
+          <t>20208000887698054001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2076,317 +2076,317 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №222/26, НДС 12%</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №638</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>83153000</v>
+        <v>7388000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
       <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="n">
-        <v>3387000</v>
+        <v>1122000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bekobod Yog' Zavodi MChJ</t>
+          <t>Yangi Hayot Mato XK</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>309487672</t>
+          <t>276362214</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000015879849001</t>
+          <t>20208000849952169001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №41/26 ОТ 20.07.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №29/26, QQS 12%</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>86540000</v>
+        <v>8510000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
-        <v>2583000</v>
+        <v>797000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Guliston Metall Servis MChJ</t>
+          <t>Farovon Metall MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>244456101</t>
+          <t>348767200</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000361411379001</t>
+          <t>20208000587984937001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7355 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №99/26, QQS 12%</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>89123000</v>
+        <v>9307000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>1226000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>6391000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Urganch Plastik AJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>304819265</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000431725759001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №153/26 от 20.07.2026</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №178/26</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>90349000</v>
+        <v>2916000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n">
-        <v>1140000</v>
-      </c>
+      <c r="C50" s="2" t="n">
+        <v>6552000</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Farg'ona Farm Savdo MChJ</t>
+          <t>Sarbon Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>310020485</t>
+          <t>355798827</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000028856635001</t>
+          <t>20208000698303857001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №185/26, НДС 12%</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №7008</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>91489000</v>
+        <v>-3636000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>4072000</v>
-      </c>
-      <c r="D51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n">
+        <v>27014000</v>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Xiva Agro MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>360222698</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000139169093001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №297/26</t>
+          <t>Оплата за товар по счет-фактуре №2537 от 24.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>87417000</v>
+        <v>23378000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n">
-        <v>1736000</v>
-      </c>
+      <c r="C52" s="2" t="n">
+        <v>9127000</v>
+      </c>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bekobod Yog' Zavodi MChJ</t>
+          <t>Chust Tekstil MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>309487672</t>
+          <t>273111718</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000015879849001</t>
+          <t>20208000892961939001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №203/26 ОТ 21.07.2026</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №237/26</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>89153000</v>
+        <v>14251000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46225</v>
+        <v>46230</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>3503000</v>
+        <v>11808000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Zafar Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>206743528</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000670275462001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №8/26, НДС 12%</t>
+          <t>Shartnoma №256/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>92656000</v>
+        <v>26059000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46225</v>
+        <v>46230</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n">
-        <v>2696000</v>
+        <v>2846000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Omad Avto Savdo MChJ</t>
+          <t>Buxoro Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>368107741</t>
+          <t>245610193</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000002668297001</t>
+          <t>20208000141137934001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2396,677 +2396,672 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №16/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №9106 от 27.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>95352000</v>
+        <v>28905000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46225</v>
+        <v>46230</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
-      <c r="C55" s="2" t="n">
-        <v>1988000</v>
-      </c>
-      <c r="D55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n">
+        <v>1983000</v>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
+          <t>Farovon Metall MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>250731117</t>
+          <t>348767200</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>20208000587984937001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №104/26</t>
+          <t>Tovar uchun to'lov, h/f №9184 27.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>93364000</v>
+        <v>30888000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46225</v>
+        <v>46230</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
-      <c r="C56" s="2" t="n">
-        <v>51184000</v>
-      </c>
-      <c r="D56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n">
+        <v>1832000</v>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Xiva Agro MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>360222698</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000139169093001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №167/26</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №160/26, QQS 12%</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>42180000</v>
+        <v>32720000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
       <c r="C57" s="2" t="n"/>
       <c r="D57" s="2" t="n">
-        <v>1579000</v>
+        <v>786000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Navoiy Savdo MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>273446376</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000277652678001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6982 23.07.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №108/26, QQS 12%</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>43759000</v>
+        <v>33506000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
-      <c r="C58" s="2" t="n">
-        <v>2100000</v>
-      </c>
-      <c r="D58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n">
+        <v>777000</v>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>НДС за июнь 2026 г.</t>
+          <t>Mahsulot uchun to'lov, shartnoma №273/26, QQS 12%</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>41659000</v>
+        <v>34283000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n">
-        <v>7454000</v>
-      </c>
+      <c r="C59" s="2" t="n">
+        <v>795000</v>
+      </c>
+      <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Nurafshon Un Mahsulotlari MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>259691263</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000985509924001</t>
+          <t>20208000698158518001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8120</t>
+          <t>Elektr energiyasi uchun to'lov iyul</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>49113000</v>
+        <v>33488000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n">
-        <v>1465000</v>
-      </c>
+      <c r="C60" s="2" t="n">
+        <v>11627000</v>
+      </c>
+      <c r="D60" s="2" t="n"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Navoiy Savdo MChJ</t>
+          <t>Chust Tekstil MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>273446376</t>
+          <t>273111718</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000277652678001</t>
+          <t>20208000892961939001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №30/26, НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №2462</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>50578000</v>
+        <v>21861000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n">
-        <v>1406000</v>
+        <v>7869000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №47/26, НДС 12%</t>
+          <t>Shartnoma №137/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>51984000</v>
+        <v>29730000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
-      <c r="C62" s="2" t="n">
-        <v>3954000</v>
-      </c>
-      <c r="D62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n">
+        <v>6489000</v>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Denov Meva Eksport MChJ</t>
+          <t>Afrosiyob Tekstil XK</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>287489417</t>
+          <t>244637602</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000726110057001</t>
+          <t>20208000765267812001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6814</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2611</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>48030000</v>
+        <v>36219000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>3037000</v>
+        <v>1480000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Farovon Metall MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>348767200</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000587984937001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №213/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9259</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>51067000</v>
+        <v>37699000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>1307000</v>
+        <v>3869000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Termiz Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>334355862</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000087595876001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №254/26 от 27.07.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7304</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>52374000</v>
+        <v>41568000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>706000</v>
+        <v>1380000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bekobod Yog' Zavodi MChJ</t>
+          <t>Afrosiyob Tekstil XK</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>309487672</t>
+          <t>244637602</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000015879849001</t>
+          <t>20208000765267812001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6668 27.07.2026, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5748 29.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>53080000</v>
+        <v>42948000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>795000</v>
+        <v>300000</v>
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>200933985</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000416981585001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov iyul</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>52285000</v>
+        <v>42648000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>4442000</v>
+        <v>13688000</v>
       </c>
       <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Denov Meva Eksport MChJ</t>
+          <t>Urganch Plastik AJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>287489417</t>
+          <t>304819265</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000726110057001</t>
+          <t>20208000431725759001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №100/26</t>
+          <t>Оплата за сырье по дог. №134/26 от 31.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>47843000</v>
+        <v>28960000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
-      <c r="C68" s="2" t="n">
-        <v>10195000</v>
-      </c>
-      <c r="D68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n">
+        <v>8510000</v>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>250731117</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №179/26</t>
+          <t>Оплата за товар по с/ф №4040 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>37648000</v>
+        <v>37470000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
-      <c r="C69" s="2" t="n">
-        <v>21005000</v>
-      </c>
-      <c r="D69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n">
+        <v>1599000</v>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Xiva Agro MChJ</t>
+          <t>Gulshan Agro MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>360222698</t>
+          <t>328193547</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000139169093001</t>
+          <t>20208000739488266001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №210</t>
+          <t>Shartnoma №120/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>16643000</v>
+        <v>39069000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46231</v>
+        <v>46237</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
       <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="n">
-        <v>4570000</v>
+        <v>944000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bekobod Yog' Zavodi MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>309487672</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000015879849001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №41/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №5938 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>21213000</v>
+        <v>40013000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46231</v>
+        <v>46237</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
       <c r="C71" s="2" t="n"/>
       <c r="D71" s="2" t="n">
-        <v>1402000</v>
+        <v>697000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bekobod Yog' Zavodi MChJ</t>
+          <t>Ishonch Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>309487672</t>
+          <t>310774150</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000015879849001</t>
+          <t>20208000266829759001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3076,77 +3071,77 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4719 от 28.07.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №191/26, QQS 12%</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>22615000</v>
+        <v>40710000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n">
-        <v>1397000</v>
-      </c>
+      <c r="C72" s="2" t="n">
+        <v>1380000</v>
+      </c>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bekobod Yog' Zavodi MChJ</t>
+          <t>Chust Tekstil MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>309487672</t>
+          <t>273111718</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000015879849001</t>
+          <t>20208000892961939001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4655 за поставленный товар</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №52/26</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>24012000</v>
+        <v>39330000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>1739000</v>
+        <v>1766000</v>
       </c>
       <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
+          <t>Chust Tekstil MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>250731117</t>
+          <t>273111718</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>20208000892961939001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3156,152 +3151,152 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTN. №13/26</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №9351</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>22273000</v>
+        <v>37564000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>2333000</v>
+        <v>3201000</v>
       </c>
       <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Shodlik Logistik XK</t>
+          <t>Ilhom Non XK</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>270757417</t>
+          <t>348941737</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000532836389001</t>
+          <t>20208000611005761001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №181/26</t>
+          <t>Оплата за транспортные услуги по дог. №145/26</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>19940000</v>
+        <v>34363000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
-      <c r="C75" s="2" t="n"/>
-      <c r="D75" s="2" t="n">
-        <v>3665000</v>
-      </c>
+      <c r="C75" s="2" t="n">
+        <v>7850000</v>
+      </c>
+      <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Chust Tekstil MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>273111718</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000892961939001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №755 от 30.07.2026, в т.ч. НДС 12%</t>
+          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №214/26</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>23605000</v>
+        <v>26513000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46233</v>
+        <v>46239</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n">
-        <v>3578000</v>
-      </c>
+      <c r="C76" s="2" t="n">
+        <v>13392000</v>
+      </c>
+      <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>235448476</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №21/26, QQS 12%</t>
+          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>27183000</v>
+        <v>13121000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46234</v>
+        <v>46240</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
-      <c r="C77" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n">
+        <v>16285000</v>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Yulduz Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3311,392 +3306,392 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №222/26, QQS 12%</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>26883000</v>
+        <v>29406000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="n">
-        <v>3812000</v>
+        <v>14865000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Farovon Metall MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>348767200</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000587984937001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №17/26 от 03.08.2026</t>
+          <t>Предоплата за товар по договору №138/26 от 06.08.2026</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>30695000</v>
+        <v>44271000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
       <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="n">
-        <v>1972000</v>
+        <v>600000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №133/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №5/26, QQS 12%</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>32667000</v>
+        <v>44871000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
-      <c r="C80" s="2" t="n">
-        <v>2572000</v>
-      </c>
-      <c r="D80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n">
+        <v>544000</v>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Denov Meva Eksport MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>287489417</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000726110057001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №28/26 от 03.08.2026, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №21/26, QQS 12%</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>30095000</v>
+        <v>45415000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n">
-        <v>3286000</v>
+        <v>24262000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bekobod Yog' Zavodi MChJ</t>
+          <t>Yangi Hayot Mato XK</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>309487672</t>
+          <t>276362214</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000015879849001</t>
+          <t>20208000849952169001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №199/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1774</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>33381000</v>
+        <v>69677000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
       <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="n">
-        <v>1145000</v>
+        <v>5690000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bekobod Yog' Zavodi MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>309487672</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000015879849001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №47 за поставленный товар</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №28/26, НДС 12%</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>34526000</v>
+        <v>75367000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
-      <c r="C83" s="2" t="n">
-        <v>2255000</v>
-      </c>
-      <c r="D83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n">
+        <v>2626000</v>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
+          <t>Afrosiyob Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>250731117</t>
+          <t>246402849</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>20208000274674310001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8381</t>
+          <t>Shartnoma №55/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>32271000</v>
+        <v>77993000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
-      <c r="C84" s="2" t="n">
-        <v>2296000</v>
-      </c>
-      <c r="D84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n">
+        <v>2359000</v>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>250731117</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1091</t>
+          <t>Shartnoma №66/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>29975000</v>
+        <v>80352000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="n">
-        <v>1440000</v>
+        <v>1231000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №193/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №263/26, QQS 12%</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>31415000</v>
+        <v>81583000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>6956000</v>
+        <v>1132000</v>
       </c>
       <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sharq Avto Ehtiyot MChJ</t>
+          <t>Oltin Vodiy Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>242565389</t>
+          <t>335080958</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000945820021001</t>
+          <t>20208000573454594001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5042</t>
+          <t>Bino ijarasi uchun to'lov avgust</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>24459000</v>
+        <v>80451000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>13392000</v>
+        <v>10300000</v>
       </c>
       <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-6310)</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>16307000223851930417</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3706,157 +3701,157 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Kredit shartnomasi L-2025-6310 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>11067000</v>
+        <v>70151000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>1132000</v>
-      </c>
-      <c r="D88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n">
+        <v>4481000</v>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Nihol Qurilish MChJ</t>
+          <t>Farovon Metall MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>318350809</t>
+          <t>348767200</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000855734545001</t>
+          <t>20208000587984937001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Арендная плата за август 2026 г. по договору №94/21</t>
+          <t>Mahsulot uchun to'lov, shartn. №272/26, QQS 12%</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>9935000</v>
+        <v>74632000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
-      <c r="C89" s="2" t="n">
-        <v>33051000</v>
-      </c>
-      <c r="D89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n">
+        <v>2106000</v>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sharq Avto Ehtiyot MChJ</t>
+          <t>Buxoro Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>242565389</t>
+          <t>245610193</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000945820021001</t>
+          <t>20208000141137934001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9250</t>
+          <t>Mahsulot uchun to'lov, shartnoma №39/26, QQS 12%</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>-23116000</v>
+        <v>76738000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="n">
-        <v>33955000</v>
+        <v>945000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bekobod Yog' Zavodi MChJ</t>
+          <t>Yangi Hayot Mato XK</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>309487672</t>
+          <t>276362214</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000015879849001</t>
+          <t>20208000849952169001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №121/26, НДС 12%</t>
+          <t>Оплата за товар по с/ф №3563 от 12.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>10839000</v>
+        <v>77683000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="n">
-        <v>3595000</v>
+        <v>4106000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Olmaliq Plastik MChJ</t>
+          <t>Farovon Metall MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>271763622</t>
+          <t>348767200</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000488499521001</t>
+          <t>20208000587984937001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3866,366 +3861,371 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5401</t>
+          <t>Shartnoma №34/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>14434000</v>
+        <v>81789000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
       <c r="C92" s="2" t="n"/>
       <c r="D92" s="2" t="n">
-        <v>2093000</v>
+        <v>1661000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Farovon Metall MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>348767200</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000587984937001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2790 за поставленный товар</t>
+          <t>Shartnoma №74/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>16527000</v>
+        <v>83450000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
       <c r="C93" s="2" t="n"/>
       <c r="D93" s="2" t="n">
-        <v>1680000</v>
+        <v>1086000</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shatnoma №227/26, QQS 12%</t>
+          <t>Shartnoma №181/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>18207000</v>
+        <v>84536000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>982000</v>
+        <v>722000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Shodlik Sut MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>314933574</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000761377438001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №108/26 от 10.08.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2003</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>19189000</v>
+        <v>85258000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
-      <c r="C95" s="2" t="n">
-        <v>10300000</v>
-      </c>
-      <c r="D95" s="2" t="n"/>
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="2" t="n">
+        <v>638000</v>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-6310)</t>
+          <t>Farovon Metall MChJ</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>348767200</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>16307000223851930417</t>
+          <t>20208000587984937001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-6310 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Mahsulot uchun to'lov, shartnoma №292/26, QQS 12%</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>8889000</v>
+        <v>85896000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46245</v>
+        <v>46251</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
       <c r="C96" s="2" t="n"/>
       <c r="D96" s="2" t="n">
-        <v>3750000</v>
+        <v>13860000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4680 за поставленный товар</t>
+          <t>Shartnoma №184/26 boyicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>12639000</v>
+        <v>99756000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
       <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="n">
-        <v>852000</v>
+        <v>2066000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Olmaliq Sut MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>284099367</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000158876980001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №101/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №124/26, QQS 12%</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>13491000</v>
+        <v>101822000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
       <c r="C98" s="2" t="n"/>
       <c r="D98" s="2" t="n">
-        <v>718000</v>
+        <v>1529000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №922 от 12.08.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №253/26, QQS 12%</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>14209000</v>
+        <v>103351000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>7621000</v>
-      </c>
-      <c r="D99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n">
+        <v>545000</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>250731117</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №85/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1456</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>6588000</v>
+        <v>103896000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n">
-        <v>647000</v>
-      </c>
+      <c r="C100" s="2" t="n">
+        <v>1826000</v>
+      </c>
+      <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №292/26, НДС 12%</t>
+          <t>Iyul oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>7235000</v>
+        <v>102070000</v>
       </c>
     </row>
     <row r="101">
@@ -4235,37 +4235,37 @@
       <c r="B101" t="n">
         <v>193</v>
       </c>
-      <c r="C101" s="2" t="n"/>
-      <c r="D101" s="2" t="n">
-        <v>12932000</v>
-      </c>
+      <c r="C101" s="2" t="n">
+        <v>1826000</v>
+      </c>
+      <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5742 от 17.08.2026, в т.ч. НДС 12%</t>
+          <t>JShDS iyul oyi uchun</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>20167000</v>
+        <v>100244000</v>
       </c>
     </row>
     <row r="102">
@@ -4275,37 +4275,37 @@
       <c r="B102" t="n">
         <v>194</v>
       </c>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="n">
-        <v>5862000</v>
-      </c>
+      <c r="C102" s="2" t="n">
+        <v>1827000</v>
+      </c>
+      <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Chust Tekstil MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>273111718</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000892961939001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Shartnoma №61/26 bo'yicha oldindan to'lov</t>
+          <t>Xom ashyo uchun to'lov, shartn. №217/26, QQS bilan</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>26029000</v>
+        <v>98417000</v>
       </c>
     </row>
     <row r="103">
@@ -4315,183 +4315,183 @@
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n">
-        <v>2968000</v>
-      </c>
+      <c r="C103" s="2" t="n">
+        <v>7474000</v>
+      </c>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Urganch Plastik AJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>304819265</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000431725759001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №487 за поставленный товар</t>
+          <t>Xom ashyo uchun to'lov, shartn. №82/26, QQS bilan</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>28997000</v>
+        <v>90943000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
       <c r="C104" s="2" t="n"/>
       <c r="D104" s="2" t="n">
-        <v>2843000</v>
+        <v>3062000</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №240/26 от 17.08.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5057</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>31840000</v>
+        <v>94005000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
-      <c r="C105" s="2" t="n"/>
-      <c r="D105" s="2" t="n">
-        <v>1534000</v>
-      </c>
+      <c r="C105" s="2" t="n">
+        <v>3304000</v>
+      </c>
+      <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Gulshan Mebel MChJ</t>
+          <t>Ilhom Non XK</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>354464028</t>
+          <t>348941737</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000952746743001</t>
+          <t>20208000611005761001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №17/26 от 17.08.2026</t>
+          <t>Оплата за сырье по дог. №252/26 от 18.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>33374000</v>
+        <v>90701000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
       <c r="C106" s="2" t="n"/>
       <c r="D106" s="2" t="n">
-        <v>1265000</v>
+        <v>653000</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №248/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6231</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>34639000</v>
+        <v>91354000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46251</v>
+        <v>46254</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
       <c r="C107" s="2" t="n"/>
       <c r="D107" s="2" t="n">
-        <v>1183000</v>
+        <v>2360000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Afrosiyob Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>246402849</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000274674310001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4501,157 +4501,157 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №259/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1861</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>35822000</v>
+        <v>93714000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46251</v>
+        <v>46254</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>1826000</v>
+        <v>5793000</v>
       </c>
       <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qarshi Qurilish XK</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>275741755</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000283638977001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июль</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №184/26</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>33996000</v>
+        <v>87921000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46251</v>
+        <v>46255</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>1826000</v>
-      </c>
-      <c r="D109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n">
+        <v>1840000</v>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Gulshan Agro MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>328193547</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000739488266001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>НДФЛ за июль 2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №151/26, QQS 12%</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>32170000</v>
+        <v>89761000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
-      <c r="C110" s="2" t="n">
-        <v>1844000</v>
-      </c>
-      <c r="D110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n">
+        <v>1498000</v>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
+          <t>Farovon Metall MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>250731117</t>
+          <t>348767200</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>20208000587984937001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №164/26</t>
+          <t>Оплата по счет-фактуре №2325 за поставленный товар</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>30326000</v>
+        <v>91259000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>2035000</v>
+        <v>1226000</v>
       </c>
       <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
+          <t>Chust Tekstil MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>250731117</t>
+          <t>273111718</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>20208000892961939001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4661,237 +4661,237 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №247/26</t>
+          <t>Tovarlar uchun to'lov h/f №881</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>28291000</v>
+        <v>90033000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n">
-        <v>8939000</v>
-      </c>
+      <c r="C112" s="2" t="n">
+        <v>1855000</v>
+      </c>
+      <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №208/26, НДС 12%</t>
+          <t>QQS iyul 2026 uchun</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>37230000</v>
+        <v>88178000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
-      <c r="C113" s="2" t="n"/>
-      <c r="D113" s="2" t="n">
-        <v>3543000</v>
-      </c>
+      <c r="C113" s="2" t="n">
+        <v>2644000</v>
+      </c>
+      <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Ilhom Non XK</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>348941737</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000611005761001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №161/26 от 20.08.2026</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №237/26</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>40773000</v>
+        <v>85534000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n">
-        <v>843000</v>
-      </c>
+      <c r="C114" s="2" t="n">
+        <v>1185000</v>
+      </c>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Navoiy Savdo MChJ</t>
+          <t>Chust Tekstil MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>273446376</t>
+          <t>273111718</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000277652678001</t>
+          <t>20208000892961939001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6684</t>
+          <t>Materiallar uchun oldindan tolov, shartnoma №40/26</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>41616000</v>
+        <v>84349000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>1844000</v>
+        <v>707000</v>
       </c>
       <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000698158518001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июль</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>39772000</v>
+        <v>83642000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>2000000</v>
+        <v>1275000</v>
       </c>
       <c r="D116" s="2" t="n"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
+          <t>Bahor Avto Savdo XK</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>250731117</t>
+          <t>222269861</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>20208000916909352001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №6/26 от 21.08.2026, НДС 12%</t>
+          <t>Предоплата за материалы по договору №193/26</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>37772000</v>
+        <v>82367000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>4897000</v>
+        <v>84756000</v>
       </c>
       <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
+          <t>Chust Tekstil MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>250731117</t>
+          <t>273111718</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>20208000892961939001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4901,117 +4901,117 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №163/26</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №143/26</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>32875000</v>
+        <v>-2389000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
       <c r="C118" s="2" t="n"/>
       <c r="D118" s="2" t="n">
-        <v>9801000</v>
+        <v>1450000</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Nurafshon Un Mahsulotlari MChJ</t>
+          <t>Buxoro Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>259691263</t>
+          <t>245610193</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000985509924001</t>
+          <t>20208000141137934001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1036 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9738</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>42676000</v>
+        <v>-939000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>5717000</v>
+        <v>668000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bekobod Yog' Zavodi MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>309487672</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000015879849001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Shartnoma №113/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №152/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>48393000</v>
+        <v>-271000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="n">
-        <v>1687000</v>
+        <v>9166000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Buxoro Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>245610193</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000141137934001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5021,952 +5021,952 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №98/26, НДС 12%</t>
+          <t>Shartnoma №146/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>50080000</v>
+        <v>8895000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
       <c r="C121" s="2" t="n"/>
       <c r="D121" s="2" t="n">
-        <v>1405000</v>
+        <v>2277000</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №3188 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №249/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>51485000</v>
+        <v>11172000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" s="2" t="n">
-        <v>1218000</v>
-      </c>
+      <c r="C122" s="2" t="n">
+        <v>1030000</v>
+      </c>
+      <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Bahor Avto Savdo XK</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>222269861</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000916909352001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9629 за поставленный товар</t>
+          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №212/26, QQS BILAN</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>52703000</v>
+        <v>10142000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
-      <c r="C123" s="2" t="n"/>
-      <c r="D123" s="2" t="n">
-        <v>982000</v>
-      </c>
+      <c r="C123" s="2" t="n">
+        <v>3245000</v>
+      </c>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Gulshan Mebel MChJ</t>
+          <t>Chust Tekstil MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>354464028</t>
+          <t>273111718</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000952746743001</t>
+          <t>20208000892961939001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5771 за поставленный товар</t>
+          <t>Tovarlar uchun to'lov h/f №5222</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>53685000</v>
+        <v>6897000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
       <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="n">
-        <v>713000</v>
+        <v>4519000</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Farovon Metall MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>348767200</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000587984937001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9508</t>
+          <t>Shartnoma №77/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>54398000</v>
+        <v>11416000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
-      <c r="C125" s="2" t="n">
-        <v>707000</v>
-      </c>
-      <c r="D125" s="2" t="n"/>
+      <c r="C125" s="2" t="n"/>
+      <c r="D125" s="2" t="n">
+        <v>2691000</v>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000416981585001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Mahsulot uchun to'lov, shartnoma №82/26, QQS 12%</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>53691000</v>
+        <v>14107000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
-      <c r="C126" s="2" t="n">
-        <v>2311000</v>
-      </c>
-      <c r="D126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n">
+        <v>1679000</v>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Denov Meva Eksport MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>287489417</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000726110057001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8067</t>
+          <t>Mahsulot uchun to'lov, shartnoma №23/26, QQS 12%</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>51380000</v>
+        <v>15786000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
-      <c r="C127" s="2" t="n">
-        <v>2668000</v>
-      </c>
-      <c r="D127" s="2" t="n"/>
+      <c r="C127" s="2" t="n"/>
+      <c r="D127" s="2" t="n">
+        <v>1642000</v>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>250731117</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №37/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №161/26, QQS 12%</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>48712000</v>
+        <v>17428000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
-      <c r="C128" s="2" t="n">
-        <v>38571000</v>
-      </c>
-      <c r="D128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n">
+        <v>1599000</v>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Shodlik Logistik XK</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>270757417</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000532836389001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9773</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №6009</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>10141000</v>
+        <v>19027000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="2" t="n">
-        <v>2272000</v>
+        <v>1449000</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Denov Meva-Sabzavot AJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>299118849</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000850814989001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №8347 за поставленный товар</t>
+          <t>Shartnoma №72/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>12413000</v>
+        <v>20476000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
       <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="n">
-        <v>1825000</v>
+        <v>1190000</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Gulshan Mebel MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>354464028</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000952746743001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №247/26 от 25.08.2026</t>
+          <t>Оплата за продукцию по договору №283/26, НДС 12%</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>14238000</v>
+        <v>21666000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="n">
-        <v>1459000</v>
+        <v>1129000</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Farovon Metall MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>348767200</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000587984937001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №149/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №252/26, QQS 12%</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>15697000</v>
+        <v>22795000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>1291000</v>
+        <v>1040000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Afrosiyob Tekstil XK</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>244637602</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000765267812001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8635</t>
+          <t>Оплата за товар по счет-фактуре №774 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>16988000</v>
+        <v>23835000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="n">
-        <v>1807000</v>
+        <v>678000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №25/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №136/26, QQS 12%</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>18795000</v>
+        <v>24513000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
-      <c r="C134" s="2" t="n"/>
-      <c r="D134" s="2" t="n">
-        <v>667000</v>
-      </c>
+      <c r="C134" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>235448476</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №5078 за поставленный товар</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>19462000</v>
+        <v>24213000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46260</v>
+        <v>46266</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
-      <c r="C135" s="2" t="n">
-        <v>4691000</v>
-      </c>
-      <c r="D135" s="2" t="n"/>
+      <c r="C135" s="2" t="n"/>
+      <c r="D135" s="2" t="n">
+        <v>19175000</v>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bekobod Plastik XK</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>296048192</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000574317257001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9959</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9268 01.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>14771000</v>
+        <v>43388000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46261</v>
+        <v>46266</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
-      <c r="C136" s="2" t="n"/>
-      <c r="D136" s="2" t="n">
-        <v>6062000</v>
-      </c>
+      <c r="C136" s="2" t="n">
+        <v>17113000</v>
+      </c>
+      <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Chust Tekstil MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>273111718</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000892961939001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №116/26 от 27.08.2026</t>
+          <t>Tovarlar uchun to'lov h/f №7828</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>20833000</v>
+        <v>26275000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46261</v>
+        <v>46268</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
-      <c r="C137" s="2" t="n">
-        <v>7340000</v>
-      </c>
-      <c r="D137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n">
+        <v>5389000</v>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>250731117</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №204/26</t>
+          <t>Shartnoma №139/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>13493000</v>
+        <v>31664000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
-      <c r="C138" s="2" t="n"/>
-      <c r="D138" s="2" t="n">
-        <v>6326000</v>
-      </c>
+      <c r="C138" s="2" t="n">
+        <v>2371000</v>
+      </c>
+      <c r="D138" s="2" t="n"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Bekobod Yog' Zavodi MChJ</t>
+          <t>Bahor Avto Savdo XK</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>309487672</t>
+          <t>222269861</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000015879849001</t>
+          <t>20208000916909352001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №9345 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за сырье по договору №137/26 от 03.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>19819000</v>
+        <v>29293000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
-      <c r="C139" s="2" t="n"/>
-      <c r="D139" s="2" t="n">
-        <v>2695000</v>
-      </c>
+      <c r="C139" s="2" t="n">
+        <v>2656000</v>
+      </c>
+      <c r="D139" s="2" t="n"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bekobod Yog' Zavodi MChJ</t>
+          <t>Urganch Plastik AJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>309487672</t>
+          <t>304819265</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000015879849001</t>
+          <t>20208000431725759001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8803 31.08.2026, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №75/26</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>22514000</v>
+        <v>26637000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="n">
-        <v>2520000</v>
+        <v>802000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Guliston Metall Servis MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>244456101</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000361411379001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Shartnoma №108/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №61/26, QQS 12%</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>25034000</v>
+        <v>27439000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
       <c r="C141" s="2" t="n"/>
       <c r="D141" s="2" t="n">
-        <v>1471000</v>
+        <v>31401000</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Mehnat Agro MChJ</t>
+          <t>Saodat Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>316281935</t>
+          <t>369126309</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000727394882001</t>
+          <t>20208000550992451001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №165/26 от 31.08.2026</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №9118</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>26505000</v>
+        <v>58840000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
       <c r="C142" s="2" t="n"/>
       <c r="D142" s="2" t="n">
-        <v>1094000</v>
+        <v>30989000</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Afrosiyob Tekstil XK</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>244637602</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000765267812001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Shartnoma №196/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №4498 за поставленный товар</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>27599000</v>
+        <v>89829000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="n">
-        <v>805000</v>
+        <v>5191000</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №20/26 от 31.08.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №191/26, QQS 12%</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>28404000</v>
+        <v>95020000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
-      <c r="C144" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D144" s="2" t="n"/>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n">
+        <v>1900000</v>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Yulduz Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -5976,117 +5976,117 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Плата за SMS-информирование</t>
+          <t>Mahsulot uchun to'lov, shartn. №61/26, QQS 12%</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>28104000</v>
+        <v>96920000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
-      <c r="C145" s="2" t="n">
-        <v>3396000</v>
-      </c>
-      <c r="D145" s="2" t="n"/>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n">
+        <v>995000</v>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Bekobod Plastik XK</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>296048192</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000574317257001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №94/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №21</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>24708000</v>
+        <v>97915000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46266</v>
+        <v>46272</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
-      <c r="C146" s="2" t="n">
-        <v>2302000</v>
-      </c>
-      <c r="D146" s="2" t="n"/>
+      <c r="C146" s="2" t="n"/>
+      <c r="D146" s="2" t="n">
+        <v>776000</v>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>250731117</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №272/26 от 01.09.2026, НДС 12%</t>
+          <t>Оплата по счет-фактуре №2675 за поставленный товар</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>22406000</v>
+        <v>98691000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46267</v>
+        <v>46272</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
       <c r="C147" s="2" t="n">
-        <v>8426000</v>
+        <v>4947000</v>
       </c>
       <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Sharq Avto Ehtiyot MChJ</t>
+          <t>Chust Tekstil MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>242565389</t>
+          <t>273111718</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000945820021001</t>
+          <t>20208000892961939001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6096,352 +6096,347 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГ. №268/26</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №244/26, QQS bilan</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>13980000</v>
+        <v>93744000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
-      <c r="C148" s="2" t="n"/>
-      <c r="D148" s="2" t="n">
-        <v>2581000</v>
-      </c>
+      <c r="C148" s="2" t="n">
+        <v>7319000</v>
+      </c>
+      <c r="D148" s="2" t="n"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Gulshan Mebel MChJ</t>
+          <t>Ilhom Non XK</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>354464028</t>
+          <t>348941737</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000952746743001</t>
+          <t>20208000611005761001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №282/26, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №73/26</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>16561000</v>
+        <v>86425000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B149" t="n">
         <v>241</v>
       </c>
       <c r="C149" s="2" t="n">
-        <v>3068000</v>
+        <v>13658000</v>
       </c>
       <c r="D149" s="2" t="n"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Xiva Agro MChJ</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>360222698</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000139169093001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №22/26 от 04.09.2026, НДС 12%</t>
+          <t>Avgust oyi uchun ish haqi, reestr №3957</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>13493000</v>
+        <v>72767000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="B150" t="n">
         <v>242</v>
       </c>
-      <c r="C150" s="2" t="n"/>
-      <c r="D150" s="2" t="n">
-        <v>6755000</v>
-      </c>
+      <c r="C150" s="2" t="n">
+        <v>1154000</v>
+      </c>
+      <c r="D150" s="2" t="n"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Olmaliq Plastik MChJ</t>
+          <t>Oltin Vodiy Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>271763622</t>
+          <t>335080958</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000488499521001</t>
+          <t>20208000573454594001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №197/26 от 07.09.2026</t>
+          <t>Ijara haqi sentyabr oyi uchun, shartnoma №25/23</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>20248000</v>
+        <v>71613000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46272</v>
+        <v>46275</v>
       </c>
       <c r="B151" t="n">
         <v>243</v>
       </c>
       <c r="C151" s="2" t="n">
-        <v>1154000</v>
+        <v>3206000</v>
       </c>
       <c r="D151" s="2" t="n"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Nihol Qurilish MChJ</t>
+          <t>Qarshi Qurilish XK</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>318350809</t>
+          <t>275741755</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000855734545001</t>
+          <t>20208000283638977001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Ijara haqi sentyabr oyi uchun, shartnoma №94/21</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №36/26, QQS bilan</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>19094000</v>
+        <v>68407000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>46272</v>
+        <v>46275</v>
       </c>
       <c r="B152" t="n">
         <v>244</v>
       </c>
       <c r="C152" s="2" t="n">
-        <v>13658000</v>
+        <v>5132000</v>
       </c>
       <c r="D152" s="2" t="n"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Bahor Avto Savdo XK</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>222269861</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000916909352001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Xom ashyo uchun to'lov, shartn. №275/26, QQS bilan</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>5436000</v>
+        <v>63275000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>46272</v>
+        <v>46275</v>
       </c>
       <c r="B153" t="n">
         <v>245</v>
       </c>
       <c r="C153" s="2" t="n">
-        <v>20377000</v>
+        <v>10300000</v>
       </c>
       <c r="D153" s="2" t="n"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Bekobod Plastik XK</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>296048192</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-6310)</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000574317257001</t>
+          <t>16307000223851930417</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №260/26</t>
+          <t>Kredit shartnomasi L-2025-6310 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>-14941000</v>
+        <v>52975000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="B154" t="n">
         <v>246</v>
       </c>
       <c r="C154" s="2" t="n"/>
       <c r="D154" s="2" t="n">
-        <v>3901000</v>
+        <v>10925000</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Farovon Metall MChJ</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>348767200</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000587984937001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №244/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №49/26, QQS 12%</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>-11040000</v>
+        <v>63900000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="B155" t="n">
         <v>247</v>
       </c>
       <c r="C155" s="2" t="n"/>
       <c r="D155" s="2" t="n">
-        <v>3427000</v>
+        <v>775000</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3311 от 08.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №25/26, НДС 12%</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>-7613000</v>
+        <v>64675000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B156" t="n">
         <v>248</v>
       </c>
       <c r="C156" s="2" t="n">
-        <v>15151000</v>
+        <v>1563000</v>
       </c>
       <c r="D156" s="2" t="n"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
+          <t>Chust Tekstil MChJ</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>250731117</t>
+          <t>273111718</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>20208000892961939001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6451,152 +6446,157 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №156/26</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №154/26, QQS bilan</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>-22764000</v>
+        <v>63112000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B157" t="n">
         <v>249</v>
       </c>
       <c r="C157" s="2" t="n"/>
       <c r="D157" s="2" t="n">
-        <v>5052000</v>
+        <v>8165000</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Termiz Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>334355862</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000087595876001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №159/26 от 10.09.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №147/26, QQS 12%</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>-17712000</v>
+        <v>71277000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B158" t="n">
         <v>250</v>
       </c>
-      <c r="C158" s="2" t="n">
-        <v>2458000</v>
-      </c>
-      <c r="D158" s="2" t="n"/>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n">
+        <v>6957000</v>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Bekobod Plastik XK</t>
+          <t>Gulshan Agro MChJ</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>296048192</t>
+          <t>328193547</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000574317257001</t>
+          <t>20208000739488266001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №1/26</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №7129</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>-20170000</v>
+        <v>78234000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B159" t="n">
         <v>251</v>
       </c>
-      <c r="C159" s="2" t="n">
-        <v>7868000</v>
-      </c>
-      <c r="D159" s="2" t="n"/>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n">
+        <v>2087000</v>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
+          <t>Farovon Metall MChJ</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>250731117</t>
+          <t>348767200</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>20208000587984937001</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8287</t>
+          <t>Оплата по счет-фактуре №9076 за поставленный товар</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>-28038000</v>
+        <v>80321000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B160" t="n">
         <v>252</v>
       </c>
-      <c r="C160" s="2" t="n">
-        <v>10300000</v>
-      </c>
-      <c r="D160" s="2" t="n"/>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="2" t="n">
+        <v>2064000</v>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-6310)</t>
+          <t>Afrosiyob Tekstil XK</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>244637602</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>16307000223851930417</t>
+          <t>20208000765267812001</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6606,11 +6606,11 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-6310 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Mahsulot uchun to'lov, shartnoma №247/26, QQS 12%</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>-38338000</v>
+        <v>82385000</v>
       </c>
     </row>
     <row r="161">
@@ -6622,35 +6622,35 @@
       </c>
       <c r="C161" s="2" t="n"/>
       <c r="D161" s="2" t="n">
-        <v>10211000</v>
+        <v>1856000</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Shartnoma №269/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №211/26, НДС 12%</t>
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>-28127000</v>
+        <v>84241000</v>
       </c>
     </row>
     <row r="162">
@@ -6662,35 +6662,35 @@
       </c>
       <c r="C162" s="2" t="n"/>
       <c r="D162" s="2" t="n">
-        <v>3938000</v>
+        <v>1774000</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №1249 от 14.09.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7220</t>
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>-24189000</v>
+        <v>86015000</v>
       </c>
     </row>
     <row r="163">
@@ -6702,40 +6702,40 @@
       </c>
       <c r="C163" s="2" t="n"/>
       <c r="D163" s="2" t="n">
-        <v>1857000</v>
+        <v>1714000</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Guliston Metall Servis MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>244456101</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>20208000361411379001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №179/26 от 14.09.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3212 14.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>-22332000</v>
+        <v>87729000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="B164" t="n">
         <v>256</v>
@@ -6766,16 +6766,16 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Социальный налог за август 2026 г.</t>
+          <t>Ijtimoiy soliq avgust 2026</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>-24194000</v>
+        <v>85867000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="B165" t="n">
         <v>257</v>
@@ -6810,127 +6810,127 @@
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>-26056000</v>
+        <v>84005000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B166" t="n">
         <v>258</v>
       </c>
       <c r="C166" s="2" t="n"/>
       <c r="D166" s="2" t="n">
-        <v>2763000</v>
+        <v>1531000</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Shartnoma №168/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9154 17.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>-23293000</v>
+        <v>85536000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B167" t="n">
         <v>259</v>
       </c>
-      <c r="C167" s="2" t="n">
-        <v>6716000</v>
-      </c>
-      <c r="D167" s="2" t="n"/>
+      <c r="C167" s="2" t="n"/>
+      <c r="D167" s="2" t="n">
+        <v>1254000</v>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>250731117</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №216/26</t>
+          <t>Shartnoma №107/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>-30009000</v>
+        <v>86790000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n">
-        <v>46286</v>
+        <v>46282</v>
       </c>
       <c r="B168" t="n">
         <v>260</v>
       </c>
-      <c r="C168" s="2" t="n"/>
-      <c r="D168" s="2" t="n">
-        <v>50636000</v>
-      </c>
+      <c r="C168" s="2" t="n">
+        <v>5851000</v>
+      </c>
+      <c r="D168" s="2" t="n"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Chust Tekstil MChJ</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>273111718</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000892961939001</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3844 за поставленный товар</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №125/26</t>
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>20627000</v>
+        <v>80939000</v>
       </c>
     </row>
     <row r="169">
@@ -6942,35 +6942,35 @@
       </c>
       <c r="C169" s="2" t="n"/>
       <c r="D169" s="2" t="n">
-        <v>3625000</v>
+        <v>7837000</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8828 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8398</t>
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>24252000</v>
+        <v>88776000</v>
       </c>
     </row>
     <row r="170">
@@ -6980,37 +6980,37 @@
       <c r="B170" t="n">
         <v>262</v>
       </c>
-      <c r="C170" s="2" t="n">
-        <v>1921000</v>
-      </c>
-      <c r="D170" s="2" t="n"/>
+      <c r="C170" s="2" t="n"/>
+      <c r="D170" s="2" t="n">
+        <v>1815000</v>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Afrosiyob Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>246402849</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000274674310001</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за август</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8388 21.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>22331000</v>
+        <v>90591000</v>
       </c>
     </row>
     <row r="171">
@@ -7020,117 +7020,117 @@
       <c r="B171" t="n">
         <v>263</v>
       </c>
-      <c r="C171" s="2" t="n">
-        <v>3077000</v>
-      </c>
-      <c r="D171" s="2" t="n"/>
+      <c r="C171" s="2" t="n"/>
+      <c r="D171" s="2" t="n">
+        <v>1489000</v>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>250731117</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №172/26 от 21.09.2026, НДС 12%</t>
+          <t>Shartnoma №258/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>19254000</v>
+        <v>92080000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="3" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B172" t="n">
         <v>264</v>
       </c>
-      <c r="C172" s="2" t="n"/>
-      <c r="D172" s="2" t="n">
-        <v>45444000</v>
-      </c>
+      <c r="C172" s="2" t="n">
+        <v>1572000</v>
+      </c>
+      <c r="D172" s="2" t="n"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Bekobod Yog' Zavodi MChJ</t>
+          <t>Chust Tekstil MChJ</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>309487672</t>
+          <t>273111718</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>20208000015879849001</t>
+          <t>20208000892961939001</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9374 от 22.09.2026, в т.ч. НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №248/26</t>
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>64698000</v>
+        <v>90508000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B173" t="n">
         <v>265</v>
       </c>
-      <c r="C173" s="2" t="n"/>
-      <c r="D173" s="2" t="n">
-        <v>2499000</v>
-      </c>
+      <c r="C173" s="2" t="n">
+        <v>11449000</v>
+      </c>
+      <c r="D173" s="2" t="n"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Guliston Metall Servis MChJ</t>
+          <t>Chust Tekstil MChJ</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>244456101</t>
+          <t>273111718</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>20208000361411379001</t>
+          <t>20208000892961939001</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №4908 ОТ 22.09.2026, В Т.Ч. НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №206/26</t>
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>67197000</v>
+        <v>79059000</v>
       </c>
     </row>
     <row r="174">
@@ -7140,63 +7140,63 @@
       <c r="B174" t="n">
         <v>266</v>
       </c>
-      <c r="C174" s="2" t="n"/>
-      <c r="D174" s="2" t="n">
-        <v>1736000</v>
-      </c>
+      <c r="C174" s="2" t="n">
+        <v>1969000</v>
+      </c>
+      <c r="D174" s="2" t="n"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №133/26, НДС 12%</t>
+          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
         </is>
       </c>
       <c r="J174" s="2" t="n">
-        <v>68933000</v>
+        <v>77090000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="3" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B175" t="n">
         <v>267</v>
       </c>
       <c r="C175" s="2" t="n">
-        <v>22605000</v>
+        <v>5697000</v>
       </c>
       <c r="D175" s="2" t="n"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
+          <t>Chust Tekstil MChJ</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>250731117</t>
+          <t>273111718</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>20208000892961939001</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -7206,171 +7206,171 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №7/26</t>
+          <t>Оплата за товары согласно счет-фактуре №842</t>
         </is>
       </c>
       <c r="J175" s="2" t="n">
-        <v>46328000</v>
+        <v>71393000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="3" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B176" t="n">
         <v>268</v>
       </c>
-      <c r="C176" s="2" t="n">
-        <v>2421000</v>
-      </c>
-      <c r="D176" s="2" t="n"/>
+      <c r="C176" s="2" t="n"/>
+      <c r="D176" s="2" t="n">
+        <v>4550000</v>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Denov Meva Eksport MChJ</t>
+          <t>Farovon Metall MChJ</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>287489417</t>
+          <t>348767200</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>20208000726110057001</t>
+          <t>20208000587984937001</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №30/26</t>
+          <t>Shartnoma №141/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J176" s="2" t="n">
-        <v>43907000</v>
+        <v>75943000</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="3" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B177" t="n">
         <v>269</v>
       </c>
-      <c r="C177" s="2" t="n">
-        <v>4083000</v>
-      </c>
-      <c r="D177" s="2" t="n"/>
+      <c r="C177" s="2" t="n"/>
+      <c r="D177" s="2" t="n">
+        <v>4378000</v>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>250731117</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8140</t>
+          <t>Mahsulot uchun to'lov, shartn. №121/26, QQS 12%</t>
         </is>
       </c>
       <c r="J177" s="2" t="n">
-        <v>39824000</v>
+        <v>80321000</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="3" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B178" t="n">
         <v>270</v>
       </c>
-      <c r="C178" s="2" t="n">
-        <v>10386000</v>
-      </c>
-      <c r="D178" s="2" t="n"/>
+      <c r="C178" s="2" t="n"/>
+      <c r="D178" s="2" t="n">
+        <v>4131000</v>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Sarbon Savdo AJ</t>
+          <t>Farovon Metall MChJ</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>250731117</t>
+          <t>348767200</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>20208000828929619001</t>
+          <t>20208000587984937001</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6422</t>
+          <t>Shartnoma №298/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J178" s="2" t="n">
-        <v>29438000</v>
+        <v>84452000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="3" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B179" t="n">
         <v>271</v>
       </c>
-      <c r="C179" s="2" t="n"/>
-      <c r="D179" s="2" t="n">
-        <v>7145000</v>
-      </c>
+      <c r="C179" s="2" t="n">
+        <v>25892000</v>
+      </c>
+      <c r="D179" s="2" t="n"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Navoiy Savdo MChJ</t>
+          <t>Urganch Plastik AJ</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>273446376</t>
+          <t>304819265</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>20208000277652678001</t>
+          <t>20208000431725759001</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №212/26 от 25.09.2026</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №252/26</t>
         </is>
       </c>
       <c r="J179" s="2" t="n">
-        <v>36583000</v>
+        <v>58560000</v>
       </c>
     </row>
     <row r="180">
@@ -7381,36 +7381,36 @@
         <v>272</v>
       </c>
       <c r="C180" s="2" t="n">
-        <v>721000</v>
+        <v>12716000</v>
       </c>
       <c r="D180" s="2" t="n"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Chust Tekstil MChJ</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>273111718</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>20208000416981585001</t>
+          <t>20208000892961939001</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №77/26</t>
         </is>
       </c>
       <c r="J180" s="2" t="n">
-        <v>35862000</v>
+        <v>45844000</v>
       </c>
     </row>
     <row r="181">
@@ -7421,22 +7421,22 @@
         <v>273</v>
       </c>
       <c r="C181" s="2" t="n">
-        <v>7331000</v>
+        <v>22402000</v>
       </c>
       <c r="D181" s="2" t="n"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Denov Meva Eksport MChJ</t>
+          <t>Bahor Avto Savdo XK</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>287489417</t>
+          <t>222269861</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>20208000726110057001</t>
+          <t>20208000916909352001</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -7446,11 +7446,11 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №1190</t>
+          <t>Оплата за сырье по дог. №70/26 от 25.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J181" s="2" t="n">
-        <v>28531000</v>
+        <v>23442000</v>
       </c>
     </row>
     <row r="182">
@@ -7462,35 +7462,35 @@
       </c>
       <c r="C182" s="2" t="n"/>
       <c r="D182" s="2" t="n">
-        <v>2804000</v>
+        <v>1368000</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3559 за поставленный товар</t>
+          <t>Shartnoma №74/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J182" s="2" t="n">
-        <v>31335000</v>
+        <v>24810000</v>
       </c>
     </row>
     <row r="183">
@@ -7500,37 +7500,37 @@
       <c r="B183" t="n">
         <v>275</v>
       </c>
-      <c r="C183" s="2" t="n">
-        <v>2036000</v>
-      </c>
-      <c r="D183" s="2" t="n"/>
+      <c r="C183" s="2" t="n"/>
+      <c r="D183" s="2" t="n">
+        <v>952000</v>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Denov Meva Eksport MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>287489417</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>20208000726110057001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №252/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №178/26, QQS 12%</t>
         </is>
       </c>
       <c r="J183" s="2" t="n">
-        <v>29299000</v>
+        <v>25762000</v>
       </c>
     </row>
     <row r="184">
@@ -7541,76 +7541,76 @@
         <v>276</v>
       </c>
       <c r="C184" s="2" t="n">
-        <v>6332000</v>
+        <v>721000</v>
       </c>
       <c r="D184" s="2" t="n"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Bekobod Plastik XK</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>296048192</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>20208000574317257001</t>
+          <t>20208000698158518001</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №72/26, QQS bilan</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
       <c r="J184" s="2" t="n">
-        <v>22967000</v>
+        <v>25041000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="3" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="B185" t="n">
         <v>277</v>
       </c>
       <c r="C185" s="2" t="n"/>
       <c r="D185" s="2" t="n">
-        <v>5679000</v>
+        <v>785000</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Yulduz Poligraf MChJ</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>235448476</t>
+          <t>344847665</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>20208000570288114001</t>
+          <t>20208000028811489001</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №76/26 от 30.09.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1110</t>
         </is>
       </c>
       <c r="J185" s="2" t="n">
-        <v>28646000</v>
+        <v>25826000</v>
       </c>
     </row>
     <row r="186">
@@ -7620,18 +7620,23 @@
       <c r="B186" t="n">
         <v>278</v>
       </c>
-      <c r="C186" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D186" s="2" t="n"/>
+      <c r="C186" s="2" t="n"/>
+      <c r="D186" s="2" t="n">
+        <v>1074000</v>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Afrosiyob Tekstil XK</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>244637602</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000765267812001</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -7641,11 +7646,11 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за сентябрь</t>
+          <t>Mahsulot uchun to'lov, shartnoma №98/26, QQS 12%</t>
         </is>
       </c>
       <c r="J186" s="2" t="n">
-        <v>28346000</v>
+        <v>26900000</v>
       </c>
     </row>
     <row r="187">
@@ -7656,32 +7661,27 @@
         <v>279</v>
       </c>
       <c r="C187" s="2" t="n">
-        <v>1746000</v>
+        <v>300000</v>
       </c>
       <c r="D187" s="2" t="n"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Nukus Agro XK</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>247285011</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>20208000089501285001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №234/26 от 30.09.2026, НДС 12%</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
       <c r="J187" s="2" t="n">
@@ -7695,10 +7695,10 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>487482000</v>
+        <v>498437000</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>488682000</v>
+        <v>499637000</v>
       </c>
     </row>
     <row r="189">
